--- a/assets/constructions/examples/ctd_arbm_tappingattachment.xlsx
+++ b/assets/constructions/examples/ctd_arbm_tappingattachment.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,145 +539,179 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TPD316-125100-L</t>
+          <t>TCS24-M22, U7/8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>YG1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Сменные втулки TPD316 к патронам TPM</t>
+          <t>TC TAP ADAPTER</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>33</v>
+      </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
-        <v>27</v>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>DCON_X_DRVS:12.5X10</t>
+          <t>DCON_X_DRVS:17x13</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>DER_TPD:316</t>
+          <t>YG1_TCS24</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>HS-12.5</t>
+          <t>TCS24</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>YG1</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>0.6</v>
+      </c>
       <c r="U2" t="n">
         <v>0</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
-        </is>
-      </c>
+          <t>2021/YG1-TOOLING</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TCS24-M10</t>
+          <t>TPE312-090071-200-ISO-M12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>YG1</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TC TAP ADAPTER</t>
+          <t>Сменные втулки TPE312 к патронам TPG</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>33</v>
+        <v>200</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>27</v>
+      </c>
       <c r="N3" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>DCON_X_DRVS:7X5.5</t>
+          <t>DCON_X_DRVS:9x7.1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>YG1_TCS24</t>
+          <t>DER_TPE:312</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>TCS24</t>
+          <t>HS-9</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>YG1</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="S3" t="inlineStr"/>
-      <c r="T3" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2021/YG1-TOOLING</t>
-        </is>
-      </c>
+          <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TPE1024-160120-55-DIN-M20</t>
+          <t>TPE1024-170130-100-JIS-M22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -691,14 +725,14 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -713,7 +747,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>DCON_X_DRVS:16X12</t>
+          <t>DCON_X_DRVS:17x13</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -723,7 +757,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>HS-16</t>
+          <t>HS-17</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -741,79 +775,91 @@
           <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
         </is>
       </c>
+      <c r="W4" t="n">
+        <v>5</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TCS12-M8</t>
+          <t>TPE1024-180145-100-DIN-M22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>YG1</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TC TAP ADAPTER</t>
+          <t>Сменные втулки TPE1024 к патронам TPG</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>14.5</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>36</v>
+      </c>
       <c r="N5" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>DCON_X_DRVS:6.2X5</t>
+          <t>DCON_X_DRVS:18x14.5</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>YG1_TCS12</t>
+          <t>DER_TPE:1024</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>TCS12</t>
+          <t>HS-18</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>YG1</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="S5" t="inlineStr"/>
-      <c r="T5" t="n">
-        <v>0.18</v>
-      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2021/YG1-TOOLING</t>
-        </is>
-      </c>
+          <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>5</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TPE1024-110090-100-JIS-PT1/4</t>
+          <t>TPE312-060045-33-JIS-M6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -823,18 +869,18 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Сменные втулки TPE1024 к патронам TPG</t>
+          <t>Сменные втулки TPE312 к патронам TPG</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -842,24 +888,24 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="N6" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>DCON_X_DRVS:11X9</t>
+          <t>DCON_X_DRVS:6x4.5</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>DER_TPE:1024</t>
+          <t>DER_TPE:312</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>HS-11</t>
+          <t>HS-6</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -877,6 +923,12 @@
           <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
         </is>
       </c>
+      <c r="W6" t="n">
+        <v>3</v>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
